--- a/data/trans_orig/KIDM_C_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_1_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>44678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69488</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78410</t>
+          <t>78275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>53069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91729</t>
+          <t>92550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101131</t>
+          <t>101226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143430</t>
+          <t>142209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153577</t>
+          <t>153137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7777</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7782</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2298</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64401</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72183</t>
+          <t>71880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,49 +1544,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>64551</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62850</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>64978</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64551</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>62680</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>64978</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>126</t>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128932</t>
+          <t>128989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136348</t>
+          <t>136306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45954</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>52453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>45355</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53644</t>
+          <t>53919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94871</t>
+          <t>94821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105154</t>
+          <t>105186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>191806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204795</t>
+          <t>204302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251394</t>
+          <t>252686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>265435</t>
+          <t>265844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>450122</t>
+          <t>449438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>467845</t>
+          <t>467985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
